--- a/uploads/students.xlsx
+++ b/uploads/students.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\projects\Python\Svsu Exam Automate\python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB76B26-23B4-475A-A98E-EB2230683E9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD4BDC2D-B24C-4FE6-A471-B74E43A2946D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{43090F7A-6575-46CB-B1D5-521F07549025}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{43090F7A-6575-46CB-B1D5-521F07549025}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="153">
   <si>
     <t>username</t>
   </si>
@@ -483,6 +483,21 @@
   </si>
   <si>
     <t>Divesh Rawat</t>
+  </si>
+  <si>
+    <t>CR2612390020352</t>
+  </si>
+  <si>
+    <t>chetna</t>
+  </si>
+  <si>
+    <t>CR2604000009072</t>
+  </si>
+  <si>
+    <t>tamanna</t>
+  </si>
+  <si>
+    <t>2001-04-18</t>
   </si>
 </sst>
 </file>
@@ -565,7 +580,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -583,6 +598,7 @@
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -917,7 +933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0C327F5-39B1-414A-A94F-4F114FD1F760}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.42578125" bestFit="1" customWidth="1"/>
@@ -1153,16 +1169,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14">
-        <v>9310081240</v>
+        <v>148</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>152</v>
       </c>
       <c r="E14" s="2">
-        <v>38054</v>
+        <v>36999</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -1170,16 +1186,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
-      </c>
-      <c r="D15">
-        <v>9667584407</v>
+        <v>150</v>
+      </c>
+      <c r="D15" s="11">
+        <v>8178714930</v>
       </c>
       <c r="E15" s="2">
-        <v>38415</v>
+        <v>37392</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -1187,29 +1203,63 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="C16" t="s">
-        <v>146</v>
+        <v>50</v>
       </c>
       <c r="D16">
-        <v>8130878992</v>
+        <v>9310081240</v>
       </c>
       <c r="E16" s="2">
-        <v>37778</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>38054</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>140</v>
+      </c>
+      <c r="C17" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17">
+        <v>9667584407</v>
+      </c>
+      <c r="E17" s="2">
+        <v>38415</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>147</v>
+      </c>
+      <c r="C18" t="s">
+        <v>146</v>
+      </c>
+      <c r="D18">
+        <v>8130878992</v>
+      </c>
+      <c r="E18" s="2">
+        <v>37778</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
         <v>141</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C19" t="s">
         <v>52</v>
       </c>
-      <c r="D17">
+      <c r="D19">
         <v>9953354774</v>
       </c>
     </row>
@@ -1221,10 +1271,29 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BFEF7D1-BBA1-4565-B6FB-A25FBB22E872}">
-  <dimension ref="A1"/>
+  <dimension ref="A8:E8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
